--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 40005-2026 artfynd.xlsx
+++ b/artfynd/A 40005-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137172562</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137173046</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137173304</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137173786</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137173933</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137174288</v>
       </c>
       <c r="B7" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137174532</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137172700</v>
       </c>
       <c r="B9" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137172742</v>
       </c>
       <c r="B10" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137172811</v>
       </c>
       <c r="B11" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137172895</v>
       </c>
       <c r="B12" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137172940</v>
       </c>
       <c r="B13" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137172959</v>
       </c>
       <c r="B14" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137172975</v>
       </c>
       <c r="B15" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137173007</v>
       </c>
       <c r="B16" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137173018</v>
       </c>
       <c r="B17" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137173054</v>
       </c>
       <c r="B18" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137173110</v>
       </c>
       <c r="B19" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137173129</v>
       </c>
       <c r="B20" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137173167</v>
       </c>
       <c r="B21" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137173220</v>
       </c>
       <c r="B22" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137173466</v>
       </c>
       <c r="B23" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137173601</v>
       </c>
       <c r="B24" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137173612</v>
       </c>
       <c r="B25" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137173622</v>
       </c>
       <c r="B26" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137173644</v>
       </c>
       <c r="B27" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137173678</v>
       </c>
       <c r="B28" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137173691</v>
       </c>
       <c r="B29" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>137173766</v>
       </c>
       <c r="B30" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>137173881</v>
       </c>
       <c r="B31" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4043,7 +4043,7 @@
         <v>137173943</v>
       </c>
       <c r="B32" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>137173948</v>
       </c>
       <c r="B33" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>137173985</v>
       </c>
       <c r="B34" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>137174009</v>
       </c>
       <c r="B35" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>137174033</v>
       </c>
       <c r="B36" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>137174086</v>
       </c>
       <c r="B37" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>137174110</v>
       </c>
       <c r="B38" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>137174280</v>
       </c>
       <c r="B39" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>137174475</v>
       </c>
       <c r="B40" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
